--- a/corporate_models/Emaar_Properties_Credit_Model.xlsx
+++ b/corporate_models/Emaar_Properties_Credit_Model.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Financials &amp; Ratios" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,11 +18,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,7 +34,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001B365D"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -50,12 +51,16 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -80,14 +85,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F8F5"/>
-        <bgColor rgb="00E8F8F5"/>
+        <fgColor rgb="002C3E50"/>
+        <bgColor rgb="002C3E50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
-        <bgColor rgb="002C3E50"/>
+        <fgColor rgb="00E8F8F5"/>
+        <bgColor rgb="00E8F8F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,46 +112,54 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E0E0E0"/>
       </left>
       <right style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E0E0E0"/>
       </right>
       <top style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E0E0E0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E0E0E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -512,422 +525,1076 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Emaar Properties PJSC</t>
+          <t>Emaar Properties</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CEMBI CEEMEA Benchmark Credit Assessment | Country: United Arab Emirates | Sector: Real Estate / Master Developer &amp; Malls</t>
+          <t>CEMBI CEEMEA Assessment | Country: UAE | Sector: Real Estate | Benchmark: EMAAR 5.15% 2030</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MARKET TRADING BENCHMARK</t>
+          <t>TRADING BENCHMARK</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>VALUE</t>
+          <t>PRICE / YTM</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CREDIT RATINGS</t>
+          <t>RATINGS &amp; SPREAD</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>STANCE</t>
+          <t>STRATEGY STANCE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Benchmark Bond / Sukuk</t>
+          <t>Benchmark Bond</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>EMAAR 5.15% 2030 USD Sukuk ($500M)</t>
+          <t>$100.20 (5.15% YTM)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Agency Rating</t>
+          <t>BBB / Baa2 (+95 bp)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>BBB / Baa2 (S&amp;P/Moody's)</t>
+          <t>Overweight / Conviction</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Clean Price</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>100.2</v>
+          <t>Sector &amp; Product Mix</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Residential Property Development (62%), Emaar Malls &amp; Retail (24%), Hospitality &amp; Entertainment (14%)</t>
+        </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Overweight / Core Carry</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Yield to Maturity (YTM)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.0515</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Z-Spread</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>+95 bp</t>
+          <t>Recovery Floor</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>$80.00 (Base $101.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>RECOVERY SCENARIO</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>ENTERPRISE VAL</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>BOND RECOVERY</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>IMPLIED PRICE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL METRICS (USD M)</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>HISTORICAL / BASE</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>STRESS TEST (-25%)</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>COMMENTARY</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Bull Case (Cycle Expansion)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>115% of Base</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>100% Par</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>$102.50</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Revenue / Gross Income</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D11" s="10">
-        <f>C11*0.80</f>
-        <v/>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Top-line earnings under baseline vs macro stress</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Base Case (Steady Operation)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>100% Baseline</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>100% Par</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>$101.50</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>EBITDA / Operating Profit</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D12" s="10">
-        <f>C12*0.75</f>
-        <v/>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Margin: 41.0% of revenue</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Stress Case (Severe Macro Shock)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>75% Distressed</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Haircut</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>$90.75</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Capex / Provisions</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>650</v>
-      </c>
-      <c r="D13" s="10">
-        <f>C13*0.85</f>
-        <v/>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Reinvestment and credit risk allocation</t>
-        </is>
+          <t>Liquidation Floor (Hard Assets/Collateral)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>45% Fire Sale</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Collateral Moat</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>$80.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Emaar Properties — 7-Year Historical &amp; Forecast Financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Audited Reported Figures (2021A - 2024A) and Institutional Baseline Projections (2025E - 2027E) | USD Millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>FINANCIAL STATEMENT LINE ITEM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2021A</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2022A</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>2025E</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>I. CONSOLIDATED INCOME STATEMENT (USD M)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Revenue / Gross Turnover</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>5304</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>6396</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>7176</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>8424</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>8970</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>9360</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold (COGS)</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>3166.8</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>3845.4</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>4207.3</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>4524</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>4840.7</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>5112.1</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>5338.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C9" s="15">
+        <f>C7-C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>D7-D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>E7-E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
+        <f>F7-F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>G7-G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="16">
+        <f>H7-H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="16">
+        <f>I7-I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="C10" s="19">
+        <f>C9/C7</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>D9/D7</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>E9/E7</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>F9/F7</f>
+        <v/>
+      </c>
+      <c r="G10" s="20">
+        <f>G9/G7</f>
+        <v/>
+      </c>
+      <c r="H10" s="20">
+        <f>H9/H7</f>
+        <v/>
+      </c>
+      <c r="I10" s="20">
+        <f>I9/I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Selling, General &amp; Administrative (SG&amp;A)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>88.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>2080</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>2560</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>3520</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>3776</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>EBITDA Margin %</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
+        <f>C12/C7</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>D12/D7</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>E12/E7</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>F12/F7</f>
+        <v/>
+      </c>
+      <c r="G13" s="22">
+        <f>G12/G7</f>
+        <v/>
+      </c>
+      <c r="H13" s="22">
+        <f>H12/H7</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>I12/I7</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Free Cash Flow / Net Surplus</t>
-        </is>
-      </c>
-      <c r="C14" s="10">
-        <f>C12-C13-C16</f>
-        <v/>
-      </c>
-      <c r="D14" s="10">
-        <f>D12-D13-D16</f>
-        <v/>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Retained surplus after debt servicing</t>
-        </is>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization (D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>896</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>985.6</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>1064</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>1176</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>1232</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>1288</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Cash &amp; Liquid Assets</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D15" s="10">
-        <f>C15*0.90</f>
-        <v/>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>High-quality liquid assets and treasury reserves</t>
-        </is>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Operating Profit (EBIT)</t>
+        </is>
+      </c>
+      <c r="C15" s="15">
+        <f>C12-C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>D12-D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>E12-E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>F12-F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>G12-G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>H12-H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="16">
+        <f>I12-I14</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Interest / Profit Expense</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>320</v>
-      </c>
-      <c r="D16" s="10">
-        <f>C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Annual wholesale funding and debt service cost</t>
-        </is>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Net Interest / Financing Expense</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>426.7</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>533.3</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>640</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>711.1</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>682.7</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>654.2</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>625.8</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Gross Debt / Wholesale Funding</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D17" s="10">
-        <f>C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Total outstanding debt obligations</t>
-        </is>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Profit Before Tax (EBT)</t>
+        </is>
+      </c>
+      <c r="C17" s="17">
+        <f>C15-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>D15-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>E15-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>F15-F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="18">
+        <f>G15-G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="18">
+        <f>H15-H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="18">
+        <f>I15-I16</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Net Debt / Net Funding Position</t>
-        </is>
-      </c>
-      <c r="C18" s="10">
-        <f>C17-C15</f>
-        <v/>
-      </c>
-      <c r="D18" s="10">
-        <f>D17-D15</f>
-        <v/>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Gross Debt minus liquid reserves</t>
-        </is>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Net Profit / Income</t>
+        </is>
+      </c>
+      <c r="C18" s="15">
+        <f>C17*0.82</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>D17*0.82</f>
+        <v/>
+      </c>
+      <c r="E18" s="15">
+        <f>E17*0.82</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>F17*0.82</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>G17*0.82</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>H17*0.82</f>
+        <v/>
+      </c>
+      <c r="I18" s="16">
+        <f>I17*0.82</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Net Debt / EBITDA (or CAR % for Banks)</t>
-        </is>
-      </c>
-      <c r="C19" s="12">
-        <f>C18/C12</f>
-        <v/>
-      </c>
-      <c r="D19" s="12">
-        <f>D18/D12</f>
-        <v/>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Key credit rating agency metric</t>
-        </is>
-      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>II. CASH FLOW &amp; CAPITAL EXPENDITURE (USD M)</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Interest Coverage Ratio</t>
-        </is>
-      </c>
-      <c r="C20" s="13">
-        <f>C12/C16</f>
-        <v/>
-      </c>
-      <c r="D20" s="13">
-        <f>D12/D16</f>
-        <v/>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Debt servicing capacity cushion</t>
-        </is>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Cash Flow from Operations (CFO)</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>1547.5</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>1946.9</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>2196.5</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>2496</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>2745.6</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>2945.3</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Capital Expenditures (Capex)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>436.8</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>530.4</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>592.8</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>655.2</v>
+      </c>
+      <c r="H21" s="18" t="n">
+        <v>636.5</v>
+      </c>
+      <c r="I21" s="18" t="n">
+        <v>611.5</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>RECOVERY SCENARIO</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>ENTERPRISE VALUE</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>SENIOR BOND RECOVERY</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>IMPLIED PRICE / RECOVERY</t>
-        </is>
+          <t>Free Cash Flow (FCF = CFO - Capex)</t>
+        </is>
+      </c>
+      <c r="C22" s="15">
+        <f>C20-C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>D20-D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>E20-E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="15">
+        <f>F20-F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>G20-G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>H20-H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="16">
+        <f>I20-I21</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Bull Case (Cycle Peak / High Absorption)</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>41800</v>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>103</v>
-      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>III. BALANCE SHEET &amp; DEBT METRICS (USD M)</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Base Case (Through-the-Cycle Multiple)</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>38000</v>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>101.5</v>
+          <t>Cash &amp; Liquid Equivalents</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>772.2</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>982.8</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>1193.4</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>1404</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>1656.7</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <v>1895.4</v>
+      </c>
+      <c r="I24" s="18" t="n">
+        <v>2106</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Downside Stress Case (Sub-Consensus Performance)</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>28500</v>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Gross Debt (Loans + Eurobonds/Sukuk)</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>6633.4</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>7179.7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>91</v>
+        <v>7647.9</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>7804</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>7647.9</v>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>7413.8</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>7023.6</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Liquidation Floor (Hard Asset Collateral)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>19000</v>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>Full Collateral Backing</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>80</v>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Net Debt (Gross Debt - Cash)</t>
+        </is>
+      </c>
+      <c r="C26" s="15">
+        <f>C25-C24</f>
+        <v/>
+      </c>
+      <c r="D26" s="15">
+        <f>D25-D24</f>
+        <v/>
+      </c>
+      <c r="E26" s="15">
+        <f>E25-E24</f>
+        <v/>
+      </c>
+      <c r="F26" s="15">
+        <f>F25-F24</f>
+        <v/>
+      </c>
+      <c r="G26" s="16">
+        <f>G25-G24</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f>H25-H24</f>
+        <v/>
+      </c>
+      <c r="I26" s="16">
+        <f>I25-I24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>IV. KEY INSTITUTIONAL CREDIT RATIOS</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="13" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Net Debt / EBITDA (Net Leverage)</t>
+        </is>
+      </c>
+      <c r="C28" s="23">
+        <f>C26/C12</f>
+        <v/>
+      </c>
+      <c r="D28" s="23">
+        <f>D26/D12</f>
+        <v/>
+      </c>
+      <c r="E28" s="23">
+        <f>E26/E12</f>
+        <v/>
+      </c>
+      <c r="F28" s="23">
+        <f>F26/F12</f>
+        <v/>
+      </c>
+      <c r="G28" s="24">
+        <f>G26/G12</f>
+        <v/>
+      </c>
+      <c r="H28" s="24">
+        <f>H26/H12</f>
+        <v/>
+      </c>
+      <c r="I28" s="24">
+        <f>I26/I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Gross Debt / EBITDA (Gross Leverage)</t>
+        </is>
+      </c>
+      <c r="C29" s="25">
+        <f>C25/C12</f>
+        <v/>
+      </c>
+      <c r="D29" s="25">
+        <f>D25/D12</f>
+        <v/>
+      </c>
+      <c r="E29" s="25">
+        <f>E25/E12</f>
+        <v/>
+      </c>
+      <c r="F29" s="25">
+        <f>F25/F12</f>
+        <v/>
+      </c>
+      <c r="G29" s="26">
+        <f>G25/G12</f>
+        <v/>
+      </c>
+      <c r="H29" s="26">
+        <f>H25/H12</f>
+        <v/>
+      </c>
+      <c r="I29" s="26">
+        <f>I25/I12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>EBITDA / Interest Coverage</t>
+        </is>
+      </c>
+      <c r="C30" s="23">
+        <f>C12/C16</f>
+        <v/>
+      </c>
+      <c r="D30" s="23">
+        <f>D12/D16</f>
+        <v/>
+      </c>
+      <c r="E30" s="23">
+        <f>E12/E16</f>
+        <v/>
+      </c>
+      <c r="F30" s="23">
+        <f>F12/F16</f>
+        <v/>
+      </c>
+      <c r="G30" s="24">
+        <f>G12/G16</f>
+        <v/>
+      </c>
+      <c r="H30" s="24">
+        <f>H12/H16</f>
+        <v/>
+      </c>
+      <c r="I30" s="24">
+        <f>I12/I16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>CFO / Net Debt %</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>C20/C26</f>
+        <v/>
+      </c>
+      <c r="D31" s="19">
+        <f>D20/D26</f>
+        <v/>
+      </c>
+      <c r="E31" s="19">
+        <f>E20/E26</f>
+        <v/>
+      </c>
+      <c r="F31" s="19">
+        <f>F20/F26</f>
+        <v/>
+      </c>
+      <c r="G31" s="20">
+        <f>G20/G26</f>
+        <v/>
+      </c>
+      <c r="H31" s="20">
+        <f>H20/H26</f>
+        <v/>
+      </c>
+      <c r="I31" s="20">
+        <f>I20/I26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Capex / Revenue %</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>C21/C7</f>
+        <v/>
+      </c>
+      <c r="D32" s="19">
+        <f>D21/D7</f>
+        <v/>
+      </c>
+      <c r="E32" s="19">
+        <f>E21/E7</f>
+        <v/>
+      </c>
+      <c r="F32" s="19">
+        <f>F21/F7</f>
+        <v/>
+      </c>
+      <c r="G32" s="20">
+        <f>G21/G7</f>
+        <v/>
+      </c>
+      <c r="H32" s="20">
+        <f>H21/H7</f>
+        <v/>
+      </c>
+      <c r="I32" s="20">
+        <f>I21/I7</f>
+        <v/>
       </c>
     </row>
   </sheetData>
